--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrLendSpecInfo003MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrLendSpecInfo003MTM.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\CQ-TZJY-0930\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14130" windowHeight="4995" tabRatio="593"/>
   </bookViews>
@@ -20,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,14 +157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>起息日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>到息日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>期限</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -246,7 +243,28 @@
     <t>11:美元节假日</t>
   </si>
   <si>
+    <t>交易场所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>12:伦敦节假日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清算速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01:T+0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02:T+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清算速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -632,7 +650,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -670,34 +688,34 @@
         <v>41</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="7" customFormat="1" ht="16.5">
@@ -708,7 +726,6 @@
       <c r="F2" s="10"/>
       <c r="H2" s="11"/>
       <c r="I2" s="12"/>
-      <c r="J2" s="8"/>
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5">
       <c r="C3" s="2"/>
@@ -717,300 +734,399 @@
       <c r="F3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="5"/>
+      <c r="K3" s="7"/>
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:15">
+      <c r="K4" s="7"/>
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:15">
+      <c r="K5" s="7"/>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:15">
+      <c r="K6" s="7"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:15">
+      <c r="K7" s="7"/>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:15">
+      <c r="K8" s="7"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:15">
+      <c r="K9" s="7"/>
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:15">
+      <c r="K10" s="7"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:15">
+      <c r="K11" s="7"/>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:15">
+      <c r="K12" s="7"/>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:15">
+      <c r="K13" s="7"/>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:15">
+      <c r="K14" s="7"/>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:15">
+      <c r="K15" s="7"/>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:15">
+      <c r="K16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="13:13">
+    <row r="17" spans="11:13">
+      <c r="K17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="13:13">
+    <row r="18" spans="11:13">
+      <c r="K18" s="7"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="13:13">
+    <row r="19" spans="11:13">
+      <c r="K19" s="7"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="13:13">
+    <row r="20" spans="11:13">
+      <c r="K20" s="7"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="13:13">
+    <row r="21" spans="11:13">
+      <c r="K21" s="7"/>
       <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="13:13">
+    <row r="22" spans="11:13">
+      <c r="K22" s="7"/>
       <c r="M22" s="7"/>
     </row>
-    <row r="23" spans="13:13">
+    <row r="23" spans="11:13">
+      <c r="K23" s="7"/>
       <c r="M23" s="7"/>
     </row>
-    <row r="24" spans="13:13">
+    <row r="24" spans="11:13">
+      <c r="K24" s="7"/>
       <c r="M24" s="7"/>
     </row>
-    <row r="25" spans="13:13">
+    <row r="25" spans="11:13">
+      <c r="K25" s="7"/>
       <c r="M25" s="7"/>
     </row>
-    <row r="26" spans="13:13">
+    <row r="26" spans="11:13">
+      <c r="K26" s="7"/>
       <c r="M26" s="7"/>
     </row>
-    <row r="27" spans="13:13">
+    <row r="27" spans="11:13">
+      <c r="K27" s="7"/>
       <c r="M27" s="7"/>
     </row>
-    <row r="28" spans="13:13">
+    <row r="28" spans="11:13">
+      <c r="K28" s="7"/>
       <c r="M28" s="7"/>
     </row>
-    <row r="29" spans="13:13">
+    <row r="29" spans="11:13">
+      <c r="K29" s="7"/>
       <c r="M29" s="7"/>
     </row>
-    <row r="30" spans="13:13">
+    <row r="30" spans="11:13">
+      <c r="K30" s="7"/>
       <c r="M30" s="7"/>
     </row>
-    <row r="31" spans="13:13">
+    <row r="31" spans="11:13">
+      <c r="K31" s="7"/>
       <c r="M31" s="7"/>
     </row>
-    <row r="32" spans="13:13">
+    <row r="32" spans="11:13">
+      <c r="K32" s="7"/>
       <c r="M32" s="7"/>
     </row>
-    <row r="33" spans="13:13">
+    <row r="33" spans="11:13">
+      <c r="K33" s="7"/>
       <c r="M33" s="7"/>
     </row>
-    <row r="34" spans="13:13">
+    <row r="34" spans="11:13">
+      <c r="K34" s="7"/>
       <c r="M34" s="7"/>
     </row>
-    <row r="35" spans="13:13">
+    <row r="35" spans="11:13">
+      <c r="K35" s="7"/>
       <c r="M35" s="7"/>
     </row>
-    <row r="36" spans="13:13">
+    <row r="36" spans="11:13">
+      <c r="K36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="13:13">
+    <row r="37" spans="11:13">
+      <c r="K37" s="7"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="13:13">
+    <row r="38" spans="11:13">
+      <c r="K38" s="7"/>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="13:13">
+    <row r="39" spans="11:13">
+      <c r="K39" s="7"/>
       <c r="M39" s="7"/>
     </row>
-    <row r="40" spans="13:13">
+    <row r="40" spans="11:13">
+      <c r="K40" s="7"/>
       <c r="M40" s="7"/>
     </row>
-    <row r="41" spans="13:13">
+    <row r="41" spans="11:13">
+      <c r="K41" s="7"/>
       <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="13:13">
+    <row r="42" spans="11:13">
+      <c r="K42" s="7"/>
       <c r="M42" s="7"/>
     </row>
-    <row r="43" spans="13:13">
+    <row r="43" spans="11:13">
+      <c r="K43" s="7"/>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="13:13">
+    <row r="44" spans="11:13">
+      <c r="K44" s="7"/>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="13:13">
+    <row r="45" spans="11:13">
+      <c r="K45" s="7"/>
       <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="13:13">
+    <row r="46" spans="11:13">
+      <c r="K46" s="7"/>
       <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="13:13">
+    <row r="47" spans="11:13">
+      <c r="K47" s="7"/>
       <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="13:13">
+    <row r="48" spans="11:13">
+      <c r="K48" s="7"/>
       <c r="M48" s="7"/>
     </row>
-    <row r="49" spans="13:13">
+    <row r="49" spans="11:13">
+      <c r="K49" s="7"/>
       <c r="M49" s="7"/>
     </row>
-    <row r="50" spans="13:13">
+    <row r="50" spans="11:13">
+      <c r="K50" s="7"/>
       <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="13:13">
+    <row r="51" spans="11:13">
+      <c r="K51" s="7"/>
       <c r="M51" s="7"/>
     </row>
-    <row r="52" spans="13:13">
+    <row r="52" spans="11:13">
+      <c r="K52" s="7"/>
       <c r="M52" s="7"/>
     </row>
-    <row r="53" spans="13:13">
+    <row r="53" spans="11:13">
+      <c r="K53" s="7"/>
       <c r="M53" s="7"/>
     </row>
-    <row r="54" spans="13:13">
+    <row r="54" spans="11:13">
+      <c r="K54" s="7"/>
       <c r="M54" s="7"/>
     </row>
-    <row r="55" spans="13:13">
+    <row r="55" spans="11:13">
+      <c r="K55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="13:13">
+    <row r="56" spans="11:13">
+      <c r="K56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="13:13">
+    <row r="57" spans="11:13">
+      <c r="K57" s="7"/>
       <c r="M57" s="7"/>
     </row>
-    <row r="58" spans="13:13">
+    <row r="58" spans="11:13">
+      <c r="K58" s="7"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="13:13">
+    <row r="59" spans="11:13">
+      <c r="K59" s="7"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="13:13">
+    <row r="60" spans="11:13">
+      <c r="K60" s="7"/>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="13:13">
+    <row r="61" spans="11:13">
+      <c r="K61" s="7"/>
       <c r="M61" s="7"/>
     </row>
-    <row r="62" spans="13:13">
+    <row r="62" spans="11:13">
+      <c r="K62" s="7"/>
       <c r="M62" s="7"/>
     </row>
-    <row r="63" spans="13:13">
+    <row r="63" spans="11:13">
+      <c r="K63" s="7"/>
       <c r="M63" s="7"/>
     </row>
-    <row r="64" spans="13:13">
+    <row r="64" spans="11:13">
+      <c r="K64" s="7"/>
       <c r="M64" s="7"/>
     </row>
-    <row r="65" spans="13:13">
+    <row r="65" spans="11:13">
+      <c r="K65" s="7"/>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="13:13">
+    <row r="66" spans="11:13">
+      <c r="K66" s="7"/>
       <c r="M66" s="7"/>
     </row>
-    <row r="67" spans="13:13">
+    <row r="67" spans="11:13">
+      <c r="K67" s="7"/>
       <c r="M67" s="7"/>
     </row>
-    <row r="68" spans="13:13">
+    <row r="68" spans="11:13">
+      <c r="K68" s="7"/>
       <c r="M68" s="7"/>
     </row>
-    <row r="69" spans="13:13">
+    <row r="69" spans="11:13">
+      <c r="K69" s="7"/>
       <c r="M69" s="7"/>
     </row>
-    <row r="70" spans="13:13">
+    <row r="70" spans="11:13">
+      <c r="K70" s="7"/>
       <c r="M70" s="7"/>
     </row>
-    <row r="71" spans="13:13">
+    <row r="71" spans="11:13">
+      <c r="K71" s="7"/>
       <c r="M71" s="7"/>
     </row>
-    <row r="72" spans="13:13">
+    <row r="72" spans="11:13">
+      <c r="K72" s="7"/>
       <c r="M72" s="7"/>
     </row>
-    <row r="73" spans="13:13">
+    <row r="73" spans="11:13">
+      <c r="K73" s="7"/>
       <c r="M73" s="7"/>
     </row>
-    <row r="74" spans="13:13">
+    <row r="74" spans="11:13">
+      <c r="K74" s="7"/>
       <c r="M74" s="7"/>
     </row>
-    <row r="75" spans="13:13">
+    <row r="75" spans="11:13">
+      <c r="K75" s="7"/>
       <c r="M75" s="7"/>
     </row>
-    <row r="76" spans="13:13">
+    <row r="76" spans="11:13">
+      <c r="K76" s="7"/>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" spans="13:13">
+    <row r="77" spans="11:13">
+      <c r="K77" s="7"/>
       <c r="M77" s="7"/>
     </row>
-    <row r="78" spans="13:13">
+    <row r="78" spans="11:13">
+      <c r="K78" s="7"/>
       <c r="M78" s="7"/>
     </row>
-    <row r="79" spans="13:13">
+    <row r="79" spans="11:13">
+      <c r="K79" s="7"/>
       <c r="M79" s="7"/>
     </row>
-    <row r="80" spans="13:13">
+    <row r="80" spans="11:13">
+      <c r="K80" s="7"/>
       <c r="M80" s="7"/>
     </row>
-    <row r="81" spans="13:13">
+    <row r="81" spans="11:13">
+      <c r="K81" s="7"/>
       <c r="M81" s="7"/>
     </row>
-    <row r="82" spans="13:13">
+    <row r="82" spans="11:13">
+      <c r="K82" s="7"/>
       <c r="M82" s="7"/>
     </row>
-    <row r="83" spans="13:13">
+    <row r="83" spans="11:13">
+      <c r="K83" s="7"/>
       <c r="M83" s="7"/>
     </row>
-    <row r="84" spans="13:13">
+    <row r="84" spans="11:13">
+      <c r="K84" s="7"/>
       <c r="M84" s="7"/>
     </row>
-    <row r="85" spans="13:13">
+    <row r="85" spans="11:13">
+      <c r="K85" s="7"/>
       <c r="M85" s="7"/>
     </row>
-    <row r="86" spans="13:13">
+    <row r="86" spans="11:13">
+      <c r="K86" s="7"/>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="13:13">
+    <row r="87" spans="11:13">
+      <c r="K87" s="7"/>
       <c r="M87" s="7"/>
     </row>
-    <row r="88" spans="13:13">
+    <row r="88" spans="11:13">
+      <c r="K88" s="7"/>
       <c r="M88" s="7"/>
     </row>
-    <row r="89" spans="13:13">
+    <row r="89" spans="11:13">
+      <c r="K89" s="7"/>
       <c r="M89" s="7"/>
     </row>
-    <row r="90" spans="13:13">
+    <row r="90" spans="11:13">
+      <c r="K90" s="7"/>
       <c r="M90" s="7"/>
     </row>
-    <row r="91" spans="13:13">
+    <row r="91" spans="11:13">
+      <c r="K91" s="7"/>
       <c r="M91" s="7"/>
     </row>
-    <row r="92" spans="13:13">
+    <row r="92" spans="11:13">
+      <c r="K92" s="7"/>
       <c r="M92" s="7"/>
     </row>
-    <row r="93" spans="13:13">
+    <row r="93" spans="11:13">
+      <c r="K93" s="7"/>
       <c r="M93" s="7"/>
     </row>
-    <row r="94" spans="13:13">
+    <row r="94" spans="11:13">
+      <c r="K94" s="7"/>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="13:13">
+    <row r="95" spans="11:13">
+      <c r="K95" s="7"/>
       <c r="M95" s="7"/>
     </row>
-    <row r="96" spans="13:13">
+    <row r="96" spans="11:13">
+      <c r="K96" s="7"/>
       <c r="M96" s="7"/>
     </row>
-    <row r="97" spans="13:13">
+    <row r="97" spans="11:13">
+      <c r="K97" s="7"/>
       <c r="M97" s="7"/>
     </row>
-    <row r="98" spans="13:13">
+    <row r="98" spans="11:13">
+      <c r="K98" s="7"/>
       <c r="M98" s="7"/>
     </row>
-    <row r="99" spans="13:13">
+    <row r="99" spans="11:13">
+      <c r="K99" s="7"/>
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="13:13">
+    <row r="100" spans="11:13">
+      <c r="K100" s="7"/>
       <c r="M100" s="7"/>
     </row>
-    <row r="101" spans="13:13">
+    <row r="101" spans="11:13">
+      <c r="K101" s="7"/>
       <c r="M101" s="7"/>
     </row>
   </sheetData>
@@ -1019,7 +1135,7 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$F$2:$F$31</xm:f>
@@ -1042,7 +1158,13 @@
           <x14:formula1>
             <xm:f>参考格式!$L$2:$L$13</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M101</xm:sqref>
+          <xm:sqref>K2:K101</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>参考格式!$M$2:$M$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1052,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="17.875" bestFit="1" customWidth="1"/>
@@ -1063,7 +1185,7 @@
     <col min="12" max="12" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1092,134 +1214,143 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>50</v>
+      </c>
+      <c r="M1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="J2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" t="s">
         <v>56</v>
       </c>
-      <c r="K2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="F3" t="s">
         <v>10</v>
       </c>
       <c r="J3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" t="s">
         <v>57</v>
       </c>
-      <c r="K3" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="F4" t="s">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="F8" t="s">
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="L10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="L11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="F12" t="s">
         <v>19</v>
       </c>
       <c r="L12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="F13" t="s">
         <v>20</v>
       </c>
       <c r="L13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="F14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="F15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:13">
       <c r="F16" t="s">
         <v>23</v>
       </c>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrLendSpecInfo003MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrLendSpecInfo003MTM.xlsx
@@ -15,7 +15,7 @@
     <sheet name="数据" sheetId="1" r:id="rId1"/>
     <sheet name="参考格式" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -264,6 +264,14 @@
   </si>
   <si>
     <t>清算速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:OTC场外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01:银行间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -735,398 +743,497 @@
       <c r="H3" s="3"/>
       <c r="I3" s="5"/>
       <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:15">
       <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:15">
       <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:15">
       <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:15">
       <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:15">
       <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:15">
       <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:15">
       <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:15">
       <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:15">
       <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:15">
       <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:15">
       <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:15">
       <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:15">
       <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="11:13">
       <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="11:13">
       <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="11:13">
       <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
     <row r="20" spans="11:13">
       <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="11:13">
       <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
       <c r="M21" s="7"/>
     </row>
     <row r="22" spans="11:13">
       <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
       <c r="M22" s="7"/>
     </row>
     <row r="23" spans="11:13">
       <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="11:13">
       <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="11:13">
       <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="11:13">
       <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
       <c r="M26" s="7"/>
     </row>
     <row r="27" spans="11:13">
       <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
       <c r="M27" s="7"/>
     </row>
     <row r="28" spans="11:13">
       <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
       <c r="M28" s="7"/>
     </row>
     <row r="29" spans="11:13">
       <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
       <c r="M29" s="7"/>
     </row>
     <row r="30" spans="11:13">
       <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
       <c r="M30" s="7"/>
     </row>
     <row r="31" spans="11:13">
       <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
       <c r="M31" s="7"/>
     </row>
     <row r="32" spans="11:13">
       <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
       <c r="M32" s="7"/>
     </row>
     <row r="33" spans="11:13">
       <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
       <c r="M33" s="7"/>
     </row>
     <row r="34" spans="11:13">
       <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
       <c r="M34" s="7"/>
     </row>
     <row r="35" spans="11:13">
       <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
       <c r="M35" s="7"/>
     </row>
     <row r="36" spans="11:13">
       <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
     <row r="37" spans="11:13">
       <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
     <row r="38" spans="11:13">
       <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
       <c r="M38" s="7"/>
     </row>
     <row r="39" spans="11:13">
       <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
       <c r="M39" s="7"/>
     </row>
     <row r="40" spans="11:13">
       <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
       <c r="M40" s="7"/>
     </row>
     <row r="41" spans="11:13">
       <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
       <c r="M41" s="7"/>
     </row>
     <row r="42" spans="11:13">
       <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
       <c r="M42" s="7"/>
     </row>
     <row r="43" spans="11:13">
       <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
       <c r="M43" s="7"/>
     </row>
     <row r="44" spans="11:13">
       <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
     <row r="45" spans="11:13">
       <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
       <c r="M45" s="7"/>
     </row>
     <row r="46" spans="11:13">
       <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
     <row r="47" spans="11:13">
       <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
       <c r="M47" s="7"/>
     </row>
     <row r="48" spans="11:13">
       <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
       <c r="M48" s="7"/>
     </row>
     <row r="49" spans="11:13">
       <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
       <c r="M49" s="7"/>
     </row>
     <row r="50" spans="11:13">
       <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
       <c r="M50" s="7"/>
     </row>
     <row r="51" spans="11:13">
       <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
       <c r="M51" s="7"/>
     </row>
     <row r="52" spans="11:13">
       <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
       <c r="M52" s="7"/>
     </row>
     <row r="53" spans="11:13">
       <c r="K53" s="7"/>
+      <c r="L53" s="7"/>
       <c r="M53" s="7"/>
     </row>
     <row r="54" spans="11:13">
       <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
       <c r="M54" s="7"/>
     </row>
     <row r="55" spans="11:13">
       <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
     <row r="56" spans="11:13">
       <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
     <row r="57" spans="11:13">
       <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
     <row r="58" spans="11:13">
       <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
     <row r="59" spans="11:13">
       <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
       <c r="M59" s="7"/>
     </row>
     <row r="60" spans="11:13">
       <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
       <c r="M60" s="7"/>
     </row>
     <row r="61" spans="11:13">
       <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
       <c r="M61" s="7"/>
     </row>
     <row r="62" spans="11:13">
       <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
       <c r="M62" s="7"/>
     </row>
     <row r="63" spans="11:13">
       <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
       <c r="M63" s="7"/>
     </row>
     <row r="64" spans="11:13">
       <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
       <c r="M64" s="7"/>
     </row>
     <row r="65" spans="11:13">
       <c r="K65" s="7"/>
+      <c r="L65" s="7"/>
       <c r="M65" s="7"/>
     </row>
     <row r="66" spans="11:13">
       <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
       <c r="M66" s="7"/>
     </row>
     <row r="67" spans="11:13">
       <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
       <c r="M67" s="7"/>
     </row>
     <row r="68" spans="11:13">
       <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
       <c r="M68" s="7"/>
     </row>
     <row r="69" spans="11:13">
       <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
       <c r="M69" s="7"/>
     </row>
     <row r="70" spans="11:13">
       <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
       <c r="M70" s="7"/>
     </row>
     <row r="71" spans="11:13">
       <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
       <c r="M71" s="7"/>
     </row>
     <row r="72" spans="11:13">
       <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
       <c r="M72" s="7"/>
     </row>
     <row r="73" spans="11:13">
       <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
       <c r="M73" s="7"/>
     </row>
     <row r="74" spans="11:13">
       <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
       <c r="M74" s="7"/>
     </row>
     <row r="75" spans="11:13">
       <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
       <c r="M75" s="7"/>
     </row>
     <row r="76" spans="11:13">
       <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
       <c r="M76" s="7"/>
     </row>
     <row r="77" spans="11:13">
       <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
       <c r="M77" s="7"/>
     </row>
     <row r="78" spans="11:13">
       <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
       <c r="M78" s="7"/>
     </row>
     <row r="79" spans="11:13">
       <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
       <c r="M79" s="7"/>
     </row>
     <row r="80" spans="11:13">
       <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
       <c r="M80" s="7"/>
     </row>
     <row r="81" spans="11:13">
       <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
       <c r="M81" s="7"/>
     </row>
     <row r="82" spans="11:13">
       <c r="K82" s="7"/>
+      <c r="L82" s="7"/>
       <c r="M82" s="7"/>
     </row>
     <row r="83" spans="11:13">
       <c r="K83" s="7"/>
+      <c r="L83" s="7"/>
       <c r="M83" s="7"/>
     </row>
     <row r="84" spans="11:13">
       <c r="K84" s="7"/>
+      <c r="L84" s="7"/>
       <c r="M84" s="7"/>
     </row>
     <row r="85" spans="11:13">
       <c r="K85" s="7"/>
+      <c r="L85" s="7"/>
       <c r="M85" s="7"/>
     </row>
     <row r="86" spans="11:13">
       <c r="K86" s="7"/>
+      <c r="L86" s="7"/>
       <c r="M86" s="7"/>
     </row>
     <row r="87" spans="11:13">
       <c r="K87" s="7"/>
+      <c r="L87" s="7"/>
       <c r="M87" s="7"/>
     </row>
     <row r="88" spans="11:13">
       <c r="K88" s="7"/>
+      <c r="L88" s="7"/>
       <c r="M88" s="7"/>
     </row>
     <row r="89" spans="11:13">
       <c r="K89" s="7"/>
+      <c r="L89" s="7"/>
       <c r="M89" s="7"/>
     </row>
     <row r="90" spans="11:13">
       <c r="K90" s="7"/>
+      <c r="L90" s="7"/>
       <c r="M90" s="7"/>
     </row>
     <row r="91" spans="11:13">
       <c r="K91" s="7"/>
+      <c r="L91" s="7"/>
       <c r="M91" s="7"/>
     </row>
     <row r="92" spans="11:13">
       <c r="K92" s="7"/>
+      <c r="L92" s="7"/>
       <c r="M92" s="7"/>
     </row>
     <row r="93" spans="11:13">
       <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
       <c r="M93" s="7"/>
     </row>
     <row r="94" spans="11:13">
       <c r="K94" s="7"/>
+      <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
     <row r="95" spans="11:13">
       <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
       <c r="M95" s="7"/>
     </row>
     <row r="96" spans="11:13">
       <c r="K96" s="7"/>
+      <c r="L96" s="7"/>
       <c r="M96" s="7"/>
     </row>
     <row r="97" spans="11:13">
       <c r="K97" s="7"/>
+      <c r="L97" s="7"/>
       <c r="M97" s="7"/>
     </row>
     <row r="98" spans="11:13">
       <c r="K98" s="7"/>
+      <c r="L98" s="7"/>
       <c r="M98" s="7"/>
     </row>
     <row r="99" spans="11:13">
       <c r="K99" s="7"/>
+      <c r="L99" s="7"/>
       <c r="M99" s="7"/>
     </row>
     <row r="100" spans="11:13">
       <c r="K100" s="7"/>
+      <c r="L100" s="7"/>
       <c r="M100" s="7"/>
     </row>
     <row r="101" spans="11:13">
       <c r="K101" s="7"/>
+      <c r="L101" s="7"/>
       <c r="M101" s="7"/>
     </row>
   </sheetData>
@@ -1135,7 +1242,7 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$F$2:$F$31</xm:f>
@@ -1166,6 +1273,12 @@
           </x14:formula1>
           <xm:sqref>M2:M1048576</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>参考格式!$N$2:$N$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>L2:L1048576</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -1174,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="17.875" bestFit="1" customWidth="1"/>
@@ -1185,7 +1298,7 @@
     <col min="12" max="12" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1225,8 +1338,11 @@
       <c r="M1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="F2" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1358,11 @@
       <c r="M2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="F3" t="s">
         <v>10</v>
       </c>
@@ -1259,8 +1378,11 @@
       <c r="M3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="F4" t="s">
         <v>11</v>
       </c>
@@ -1268,7 +1390,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="F5" t="s">
         <v>12</v>
       </c>
@@ -1276,7 +1398,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="F6" t="s">
         <v>13</v>
       </c>
@@ -1284,7 +1406,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="F7" t="s">
         <v>14</v>
       </c>
@@ -1292,7 +1414,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="F8" t="s">
         <v>15</v>
       </c>
@@ -1300,7 +1422,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="F9" t="s">
         <v>16</v>
       </c>
@@ -1308,7 +1430,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="F10" t="s">
         <v>17</v>
       </c>
@@ -1316,7 +1438,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="F11" t="s">
         <v>18</v>
       </c>
@@ -1324,7 +1446,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="F12" t="s">
         <v>19</v>
       </c>
@@ -1332,7 +1454,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="F13" t="s">
         <v>20</v>
       </c>
@@ -1340,17 +1462,17 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:14">
       <c r="F14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="F15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="F16" t="s">
         <v>23</v>
       </c>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrLendSpecInfo003MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrLendSpecInfo003MTM.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
   <si>
     <t>序号</t>
   </si>
@@ -23,7 +23,7 @@
     <t>指令开始日</t>
   </si>
   <si>
-    <t>指令结束日</t>
+    <t>指令终止日</t>
   </si>
   <si>
     <t>组合代码</t>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>指令终止日</t>
   </si>
   <si>
     <t>资产代码</t>
@@ -229,10 +226,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -267,6 +264,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -275,9 +280,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -289,7 +302,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,6 +316,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -311,35 +332,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -348,6 +340,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -356,11 +355,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -372,17 +378,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -395,21 +407,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -420,25 +417,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,13 +561,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -468,133 +579,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -629,6 +626,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -640,15 +646,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -671,8 +668,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -682,6 +679,17 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -700,17 +708,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -719,10 +716,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -731,133 +728,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1843,22 +1840,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
         <v>6</v>
       </c>
       <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
         <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
       </c>
       <c r="I1" t="s">
         <v>14</v>
@@ -1881,212 +1878,212 @@
     </row>
     <row r="2" spans="6:14">
       <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>22</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>23</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="6:14">
       <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
         <v>25</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>27</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>28</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="6:12">
       <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
         <v>31</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="6:12">
       <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
         <v>33</v>
-      </c>
-      <c r="L5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="6:12">
       <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" t="s">
         <v>35</v>
-      </c>
-      <c r="L6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="6:12">
       <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
         <v>37</v>
-      </c>
-      <c r="L7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="6:12">
       <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" t="s">
         <v>39</v>
-      </c>
-      <c r="L8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9" spans="6:12">
       <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" t="s">
         <v>41</v>
-      </c>
-      <c r="L9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="6:12">
       <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" t="s">
         <v>43</v>
-      </c>
-      <c r="L10" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="6:12">
       <c r="F11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" t="s">
         <v>45</v>
-      </c>
-      <c r="L11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="6:12">
       <c r="F12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L12" t="s">
         <v>47</v>
-      </c>
-      <c r="L12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13" spans="6:12">
       <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" t="s">
         <v>49</v>
-      </c>
-      <c r="L13" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="6:6">
       <c r="F14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="6:6">
       <c r="F15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="6:6">
       <c r="F16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="6:6">
       <c r="F17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="6:6">
       <c r="F18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="6:6">
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="6:6">
       <c r="F20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="6:6">
       <c r="F21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="6:6">
       <c r="F22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="6:6">
       <c r="F23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="6:6">
       <c r="F24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="6:6">
       <c r="F25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="6:6">
       <c r="F26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="6:6">
       <c r="F27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="6:6">
       <c r="F28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="6:6">
       <c r="F29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="6:6">
       <c r="F30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="6:6">
       <c r="F31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
